--- a/keywords.xlsx
+++ b/keywords.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristineullebo/Documents/HON2200-datadrevne-prosjekter/prosjekt-del2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristineullebo/Documents/GitHub/HON2200-Prosjekt-2-Gruppe-H/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0FF0EB-C75F-2D42-8722-0FE1ABEF00FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC128712-FB2A-F440-A8EA-267C33D6ECD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="23840" windowHeight="11920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
